--- a/jira_export_2026-10-20.xlsx
+++ b/jira_export_2026-10-20.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>29,554 €</t>
+          <t>32,202 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>7,885 €</t>
+          <t>10,282 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>21,669 €</t>
+          <t>21,919 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1261,7 +1261,7 @@
         <v>2000</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
         <v>3000</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>0</v>
+        <v>638.25</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>0</v>
+        <v>1276.5</v>
       </c>
     </row>
     <row r="24">
@@ -5622,27 +5622,27 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5662,44 +5662,44 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O69" s="16" t="n">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="O69" s="12" t="n">
+        <v>465.85</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>0</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5734,59 +5734,59 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="O70" s="15" t="n">
-        <v>465.85</v>
+        <v>552</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>58.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5813,22 +5813,22 @@
         <v>4</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>552</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5838,32 +5838,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5878,29 +5878,29 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5910,27 +5910,27 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5945,35 +5945,35 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O73" s="16" t="n">
-        <v>0</v>
+        <v>424.8</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
@@ -5982,27 +5982,27 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6033,19 +6033,19 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>424.8</v>
+        <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6054,32 +6054,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6105,16 +6105,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>203.5</v>
+        <v>171.4</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6126,27 +6126,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6177,16 +6177,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>171.4</v>
+        <v>400</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6198,32 +6198,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6249,19 +6249,19 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>400</v>
+        <v>6177.52</v>
       </c>
       <c r="O77" s="16" t="n">
-        <v>0</v>
+        <v>2504.4</v>
       </c>
       <c r="P77" s="12" t="n">
         <v>0</v>
@@ -6270,27 +6270,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
@@ -6321,19 +6321,19 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>6177.52</v>
+        <v>500</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>2504.4</v>
+        <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
         <v>0</v>
@@ -6342,32 +6342,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6382,44 +6382,44 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O79" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>112.38</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr">
@@ -6454,69 +6454,61 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33315</t>
-        </is>
-      </c>
-      <c r="M80" s="14" t="inlineStr">
-        <is>
-          <t>00167138</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
       <c r="N80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>112.38</v>
+        <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>56.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -6526,21 +6518,29 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr"/>
-      <c r="M81" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33272</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>00166910</t>
+        </is>
+      </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6550,27 +6550,27 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
@@ -6601,16 +6601,16 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>240</v>
+        <v>149</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6622,32 +6622,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6657,38 +6657,38 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>149</v>
+        <v>337.5</v>
       </c>
       <c r="O83" s="16" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="P83" s="12" t="n">
-        <v>0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="84">
@@ -6745,53 +6745,53 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>337.5</v>
+        <v>320</v>
       </c>
       <c r="O84" s="16" t="n">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6801,35 +6801,35 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>320</v>
-      </c>
-      <c r="O85" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>1047</v>
       </c>
       <c r="P85" s="12" t="n">
         <v>0</v>
@@ -6838,32 +6838,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6873,35 +6873,35 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
-        <v>1047</v>
+        <v>400</v>
+      </c>
+      <c r="O86" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
         <v>0</v>
@@ -6910,32 +6910,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6957,20 +6957,20 @@
         <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6982,32 +6982,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7017,34 +7017,34 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7054,32 +7054,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -7101,22 +7101,22 @@
         <v>6</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>680.8</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7126,12 +7126,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
@@ -7177,16 +7177,16 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>680.8</v>
+        <v>2614.5</v>
       </c>
       <c r="O90" s="16" t="n">
         <v>0</v>
@@ -7198,32 +7198,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7233,32 +7233,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>2614.5</v>
+        <v>403.074</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7270,32 +7270,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
@@ -7317,23 +7317,23 @@
         <v>6</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>403.074</v>
-      </c>
-      <c r="O92" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
+        <v>276</v>
       </c>
       <c r="P92" s="15" t="n">
         <v>0</v>
@@ -7342,32 +7342,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
@@ -7393,19 +7393,19 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
-        <v>276</v>
+        <v>142.1</v>
+      </c>
+      <c r="O93" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
         <v>0</v>
@@ -7414,32 +7414,32 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7449,35 +7449,35 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K94" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>142.1</v>
+        <v>11278.05</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>0</v>
+        <v>233.5</v>
       </c>
       <c r="P94" s="15" t="n">
         <v>0</v>
@@ -7486,32 +7486,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7537,19 +7537,19 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>11278.05</v>
+        <v>1000</v>
       </c>
       <c r="O95" s="16" t="n">
-        <v>233.5</v>
+        <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
         <v>0</v>
@@ -7558,32 +7558,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
@@ -7609,16 +7609,16 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="O96" s="16" t="n">
         <v>0</v>
@@ -7630,12 +7630,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7645,12 +7645,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
@@ -7681,16 +7681,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7702,32 +7702,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7737,69 +7737,69 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>450</v>
+        <v>910</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -7809,64 +7809,64 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>910</v>
+        <v>4050</v>
       </c>
       <c r="O99" s="16" t="n">
-        <v>318.5</v>
+        <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
@@ -7897,16 +7897,16 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>4050</v>
+        <v>1050</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7918,27 +7918,27 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7969,16 +7969,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1050</v>
+        <v>433.5</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7990,32 +7990,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8025,34 +8025,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8062,32 +8062,32 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
@@ -8097,34 +8097,34 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>285</v>
+      </c>
+      <c r="O103" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8134,32 +8134,32 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -8174,27 +8174,27 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>285</v>
+        <v>120</v>
       </c>
       <c r="O104" s="16" t="n">
         <v>0</v>
@@ -8206,32 +8206,32 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -8241,32 +8241,32 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8278,27 +8278,27 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K106" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>210</v>
+        <v>203.5</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8350,32 +8350,32 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
@@ -8401,16 +8401,16 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>203.5</v>
+        <v>1088.5</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8422,32 +8422,32 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
@@ -8473,16 +8473,16 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>1088.5</v>
+        <v>130</v>
       </c>
       <c r="O108" s="16" t="n">
         <v>0</v>
@@ -8494,12 +8494,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
@@ -8545,16 +8545,16 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O109" s="16" t="n">
         <v>0</v>
@@ -8566,12 +8566,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
@@ -8617,16 +8617,16 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O110" s="16" t="n">
         <v>0</v>
@@ -8638,12 +8638,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
@@ -8689,16 +8689,16 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O111" s="16" t="n">
         <v>0</v>
@@ -8710,12 +8710,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
@@ -8750,27 +8750,27 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K112" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="O112" s="16" t="n">
         <v>0</v>
@@ -8782,32 +8782,32 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -8817,32 +8817,32 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="O113" s="16" t="n">
         <v>0</v>
@@ -8854,12 +8854,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -8894,29 +8894,29 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8926,27 +8926,27 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -8973,22 +8973,22 @@
         <v>9</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>7.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O115" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8998,28 +8998,26 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v/>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -9038,29 +9036,29 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9070,12 +9068,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9085,7 +9083,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
+          <t>COMMUNE DE BOBIGNY</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9103,34 +9101,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="O117" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9140,12 +9138,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9155,11 +9153,13 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E118" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -9178,27 +9178,27 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>401.54</v>
+        <v>275</v>
       </c>
       <c r="O118" s="16" t="n">
         <v>0</v>
@@ -9261,18 +9261,18 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>275</v>
-      </c>
-      <c r="O119" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9333,22 +9333,22 @@
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="15" t="n">
-        <v>0</v>
+        <v>1790</v>
+      </c>
+      <c r="O120" s="16" t="n">
+        <v>895</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>0</v>
+        <v>526.47</v>
       </c>
     </row>
     <row r="121">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O121" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
-        <v>526.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9498,12 +9498,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9513,13 +9513,11 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v/>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -9538,29 +9536,29 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>1.7</v>
+        <v>4.25</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O123" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9570,12 +9568,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9585,7 +9583,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9603,32 +9601,32 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>4.25</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="O124" s="16" t="n">
         <v>0</v>
@@ -9640,26 +9638,28 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9673,34 +9673,34 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="O125" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9710,12 +9710,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9725,13 +9725,11 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v/>
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
@@ -9745,49 +9743,49 @@
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="15" t="n">
-        <v>0</v>
+        <v>3016.08</v>
+      </c>
+      <c r="O126" s="16" t="n">
+        <v>2178.28</v>
       </c>
       <c r="P126" s="15" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9797,7 +9795,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9820,54 +9818,54 @@
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>10.5</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>3016.08</v>
+        <v>1200</v>
       </c>
       <c r="O127" s="16" t="n">
-        <v>418.9</v>
+        <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
-        <v>39.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9885,32 +9883,32 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.75</v>
+        <v>9</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>1200</v>
+        <v>3919.06</v>
       </c>
       <c r="O128" s="16" t="n">
         <v>0</v>
@@ -9922,12 +9920,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9937,7 +9935,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9960,29 +9958,29 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
-        <v>3919.06</v>
-      </c>
-      <c r="O129" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
@@ -9992,12 +9990,12 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -10007,7 +10005,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10030,7 +10028,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
@@ -10041,12 +10039,12 @@
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10111,12 +10109,12 @@
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10147,7 +10145,7 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10181,12 +10179,12 @@
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
@@ -10217,7 +10215,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10251,12 +10249,12 @@
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
@@ -10272,22 +10270,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10305,28 +10303,28 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
@@ -10342,12 +10340,12 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10357,7 +10355,7 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10375,28 +10373,28 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
@@ -10412,22 +10410,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10445,34 +10443,34 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="O136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="15" t="n">
@@ -10482,22 +10480,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10520,27 +10518,27 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
         <v>18</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N137" s="12" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="O137" s="16" t="n">
         <v>0</v>
@@ -10552,12 +10550,12 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
@@ -10567,7 +10565,7 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10585,34 +10583,34 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N138" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O138" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="15" t="n">
@@ -10622,12 +10620,12 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10637,7 +10635,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10660,23 +10658,23 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N139" s="12" t="n">
@@ -10692,12 +10690,12 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
@@ -10707,11 +10705,13 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
@@ -10720,35 +10720,27 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M140" s="14" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10762,28 +10754,26 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CD 74 - HAUTE SAVOIE</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v/>
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
@@ -10802,14 +10792,14 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L141" s="11" t="inlineStr"/>
       <c r="M141" s="11" t="inlineStr"/>
@@ -10826,22 +10816,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10859,7 +10849,7 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
@@ -10871,7 +10861,7 @@
         <v>22</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L142" s="14" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -10888,22 +10878,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10911,36 +10901,44 @@
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O143" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
@@ -10950,22 +10948,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10973,7 +10971,7 @@
       </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
@@ -10983,34 +10981,34 @@
       </c>
       <c r="H144" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M144" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N144" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="15" t="n">
@@ -11020,22 +11018,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11048,7 +11046,7 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -11058,25 +11056,17 @@
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="12" t="n">
         <v>0</v>
       </c>
@@ -11090,12 +11080,12 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
@@ -11105,7 +11095,7 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11128,14 +11118,14 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L146" s="14" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -11152,22 +11142,22 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11190,14 +11180,14 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L147" s="11" t="inlineStr"/>
       <c r="M147" s="11" t="inlineStr"/>
@@ -11214,12 +11204,12 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
@@ -11229,7 +11219,7 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11247,19 +11237,19 @@
       </c>
       <c r="H148" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -11276,12 +11266,12 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
@@ -11291,7 +11281,7 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11304,27 +11294,35 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr"/>
-      <c r="M149" s="11" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N149" s="12" t="n">
         <v>0</v>
       </c>
@@ -11338,22 +11336,22 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11366,35 +11364,23 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H150" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L150" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M150" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
       <c r="N150" s="15" t="n">
         <v>0</v>
       </c>
@@ -11408,12 +11394,12 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -11423,7 +11409,7 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11439,20 +11425,32 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H151" s="11" t="inlineStr"/>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L151" s="11" t="inlineStr"/>
-      <c r="M151" s="11" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N151" s="12" t="n">
         <v>0</v>
       </c>
@@ -11466,22 +11464,22 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD06] Littéralis expert</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11494,33 +11492,29 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H152" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="L152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M152" s="14" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N152" s="15" t="n">
@@ -11536,26 +11530,24 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
-        </is>
-      </c>
-      <c r="C153" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
-        </is>
-      </c>
-      <c r="E153" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
@@ -11564,31 +11556,27 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H153" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11602,25 +11590,21 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E154" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr"/>
       <c r="F154" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11628,24 +11612,20 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H154" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L154" s="14" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -11662,18 +11642,18 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr"/>
@@ -11690,11 +11670,11 @@
       <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" s="11" t="n">
         <v>0.25</v>
@@ -11714,18 +11694,18 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr"/>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr"/>
@@ -11742,7 +11722,7 @@
       <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
@@ -11766,18 +11746,18 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr"/>
@@ -11788,27 +11768,35 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K157" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="inlineStr"/>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N157" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O157" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P157" s="12" t="n">
@@ -11818,18 +11806,18 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr"/>
@@ -11840,13 +11828,13 @@
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
@@ -11855,20 +11843,12 @@
       <c r="K158" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L158" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M158" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L158" s="14" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
       <c r="N158" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O158" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P158" s="15" t="n">
@@ -11878,18 +11858,18 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11900,13 +11880,13 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
@@ -11915,8 +11895,16 @@
       <c r="K159" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L159" s="11" t="inlineStr"/>
-      <c r="M159" s="11" t="inlineStr"/>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
@@ -11930,18 +11918,18 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11952,31 +11940,23 @@
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M160" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
@@ -11990,18 +11970,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -12018,14 +11998,14 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L161" s="11" t="inlineStr"/>
       <c r="M161" s="11" t="inlineStr"/>
@@ -12042,18 +12022,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12070,14 +12050,14 @@
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="L162" s="14" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -12094,18 +12074,18 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12116,23 +12096,31 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N163" s="12" t="n">
         <v>0</v>
       </c>
@@ -12146,18 +12134,18 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12174,23 +12162,23 @@
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34335</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M164" s="14" t="inlineStr">
         <is>
-          <t>00168072</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N164" s="15" t="n">
@@ -12206,18 +12194,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12228,31 +12216,23 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M165" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr"/>
+      <c r="M165" s="11" t="inlineStr"/>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
@@ -12266,18 +12246,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12294,11 +12274,11 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K166" s="14" t="n">
         <v>0.25</v>
@@ -12318,18 +12298,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12340,23 +12320,31 @@
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L167" s="11" t="inlineStr"/>
-      <c r="M167" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L167" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
       <c r="N167" s="12" t="n">
         <v>0</v>
       </c>
@@ -12370,18 +12358,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12392,31 +12380,23 @@
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K168" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L168" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M168" s="14" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
+      <c r="L168" s="14" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
       <c r="N168" s="15" t="n">
         <v>0</v>
       </c>
@@ -12428,83 +12408,31 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C169" s="11" t="inlineStr"/>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E169" s="11" t="inlineStr"/>
-      <c r="F169" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G169" s="11" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H169" s="11" t="inlineStr"/>
-      <c r="I169" s="11" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J169" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K169" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L169" s="11" t="inlineStr"/>
-      <c r="M169" s="11" t="inlineStr"/>
-      <c r="N169" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O169" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="17" t="inlineStr">
+      <c r="A169" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B170" s="17" t="inlineStr"/>
-      <c r="C170" s="17" t="inlineStr"/>
-      <c r="D170" s="17" t="inlineStr"/>
-      <c r="E170" s="17" t="inlineStr"/>
-      <c r="F170" s="17" t="inlineStr"/>
-      <c r="G170" s="17" t="inlineStr"/>
-      <c r="H170" s="17" t="inlineStr"/>
-      <c r="I170" s="17" t="inlineStr"/>
-      <c r="J170" s="17" t="inlineStr"/>
-      <c r="K170" s="17" t="inlineStr"/>
-      <c r="L170" s="17" t="inlineStr"/>
-      <c r="M170" s="17" t="inlineStr"/>
-      <c r="N170" s="18" t="n">
-        <v>118715.667</v>
-      </c>
-      <c r="O170" s="18" t="n">
-        <v>29554.172</v>
-      </c>
-      <c r="P170" s="18" t="n">
-        <v>126.12</v>
+      <c r="B169" s="17" t="inlineStr"/>
+      <c r="C169" s="17" t="inlineStr"/>
+      <c r="D169" s="17" t="inlineStr"/>
+      <c r="E169" s="17" t="inlineStr"/>
+      <c r="F169" s="17" t="inlineStr"/>
+      <c r="G169" s="17" t="inlineStr"/>
+      <c r="H169" s="17" t="inlineStr"/>
+      <c r="I169" s="17" t="inlineStr"/>
+      <c r="J169" s="17" t="inlineStr"/>
+      <c r="K169" s="17" t="inlineStr"/>
+      <c r="L169" s="17" t="inlineStr"/>
+      <c r="M169" s="17" t="inlineStr"/>
+      <c r="N169" s="18" t="n">
+        <v>116825.667</v>
+      </c>
+      <c r="O169" s="18" t="n">
+        <v>32201.802</v>
+      </c>
+      <c r="P169" s="18" t="n">
+        <v>137.42</v>
       </c>
     </row>
   </sheetData>
@@ -12674,7 +12602,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId165"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14010,16 +13937,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>487711</v>
+        <v>485063</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>203308</v>
+        <v>202420</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>284402</v>
+        <v>282643</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>226067</v>
+        <v>224307</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14035,16 +13962,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>259022</v>
+        <v>256624</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>68425</v>
+        <v>67787</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>190597</v>
+        <v>188837</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>171385</v>
+        <v>169625</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -14060,10 +13987,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>225589</v>
+        <v>225339</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>131783</v>
+        <v>131533</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>93806</v>

--- a/jira_export_2026-10-20.xlsx
+++ b/jira_export_2026-10-20.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>32,202 €</t>
+          <t>34,839 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>10,282 €</t>
+          <t>11,173 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>21,919 €</t>
+          <t>23,666 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>355 h</t>
+          <t>365 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,12 +933,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>577.5</v>
+        <v>231</v>
       </c>
       <c r="O9" s="16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1607,16 +1607,8 @@
       <c r="K12" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-36034</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="inlineStr">
-        <is>
-          <t>00183131</t>
-        </is>
-      </c>
+      <c r="L12" s="14" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
       <c r="N12" s="15" t="n">
         <v>0</v>
       </c>
@@ -1690,7 +1682,7 @@
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2600</v>
+        <v>323.6</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1712,7 +1704,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -1834,9 +1826,9 @@
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>4716</v>
-      </c>
-      <c r="O15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1909,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="17">
@@ -2050,13 +2042,13 @@
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>1412.5</v>
+        <v>706.25</v>
       </c>
       <c r="O18" s="16" t="n">
-        <v>0</v>
+        <v>282.5</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0</v>
+        <v>376.67</v>
       </c>
     </row>
     <row r="19">
@@ -2402,7 +2394,7 @@
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>638.25</v>
@@ -2618,13 +2610,13 @@
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>805.5</v>
+        <v>200</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>0</v>
+        <v>119.33</v>
       </c>
     </row>
     <row r="27">
@@ -2677,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -2696,7 +2688,7 @@
         <v>3331.05</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>832.76</v>
+        <v>666.21</v>
       </c>
     </row>
     <row r="28">
@@ -2885,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
@@ -2898,13 +2890,13 @@
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>1470.38</v>
+        <v>703.398</v>
       </c>
       <c r="O30" s="16" t="n">
-        <v>238.44</v>
+        <v>437.14</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>50.2</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="31">
@@ -3117,10 +3109,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34">
@@ -3156,7 +3148,7 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -3394,7 +3386,7 @@
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="O37" s="12" t="n">
         <v>394</v>
@@ -3610,7 +3602,7 @@
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>960</v>
+        <v>480</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3766,32 +3758,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3801,12 +3793,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3817,16 +3809,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>243.6</v>
+        <v>2763.25</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3838,12 +3830,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3853,7 +3845,7 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
@@ -3885,37 +3877,37 @@
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>2763.25</v>
-      </c>
-      <c r="O44" s="16" t="n">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="O44" s="15" t="n">
+        <v>516</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3957,11 +3949,11 @@
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -3970,44 +3962,44 @@
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>129</v>
+        <v>466.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4017,34 +4009,34 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="15" t="n">
@@ -4054,32 +4046,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4089,7 +4081,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -4101,37 +4093,37 @@
         <v>3</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1.75</v>
+        <v>4.25</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>0</v>
+        <v>990</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>585</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>0</v>
+        <v>137.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4141,12 +4133,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4161,69 +4153,69 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>990</v>
-      </c>
-      <c r="O48" s="16" t="n">
-        <v>585</v>
+        <v>0</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>910</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>137.65</v>
+        <v>303.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4233,69 +4225,69 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>303.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4305,32 +4297,32 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>344</v>
+        <v>153.9</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4342,27 +4334,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4389,20 +4381,20 @@
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>153.9</v>
+        <v>4150</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,27 +4406,27 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4444,7 +4436,7 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
@@ -4454,29 +4446,21 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34310</t>
-        </is>
-      </c>
-      <c r="M52" s="14" t="inlineStr">
-        <is>
-          <t>00171605</t>
-        </is>
-      </c>
+        <v>7.75</v>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
       <c r="N52" s="15" t="n">
-        <v>4150</v>
-      </c>
-      <c r="O52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
@@ -4486,27 +4470,27 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4516,7 +4500,7 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -4533,14 +4517,22 @@
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="L53" s="11" t="inlineStr"/>
-      <c r="M53" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34258</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>00171361</t>
+        </is>
+      </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O53" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
@@ -4550,32 +4542,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4585,69 +4577,69 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>2500</v>
+        <v>1440</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>0</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4657,49 +4649,49 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2649.6</v>
+        <v>175</v>
       </c>
       <c r="O55" s="16" t="n">
-        <v>1152</v>
+        <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>70.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4709,12 +4701,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4729,7 +4721,7 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
@@ -4741,67 +4733,67 @@
         <v>4</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>175</v>
+        <v>775.6</v>
       </c>
       <c r="O56" s="16" t="n">
-        <v>0</v>
+        <v>692.5</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>0</v>
+        <v>230.83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4813,86 +4805,86 @@
         <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L57" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34201</t>
-        </is>
-      </c>
-      <c r="M57" s="11" t="inlineStr">
-        <is>
-          <t>00171162</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
       <c r="N57" s="12" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="O57" s="16" t="n">
-        <v>692.5</v>
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>230.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L58" s="14" t="inlineStr"/>
-      <c r="M58" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr">
+        <is>
+          <t>2026-0210095</t>
+        </is>
+      </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
+        <v>5388.936</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4902,27 +4894,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4942,7 +4934,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4953,19 +4945,19 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>5388.936</v>
-      </c>
-      <c r="O59" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>177.5</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
@@ -4974,27 +4966,27 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5009,12 +5001,12 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
@@ -5025,19 +5017,19 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15" t="n">
-        <v>177.5</v>
+        <v>1700</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
         <v>0</v>
@@ -5046,27 +5038,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5081,64 +5073,64 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1700</v>
+        <v>1786.1</v>
       </c>
       <c r="O61" s="16" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5158,64 +5150,64 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>1786.1</v>
+        <v>170</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>909.9</v>
+        <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5225,64 +5217,64 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>170</v>
+        <v>3000</v>
       </c>
       <c r="O63" s="16" t="n">
-        <v>0</v>
+        <v>1242.9</v>
       </c>
       <c r="P63" s="12" t="n">
-        <v>0</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5309,57 +5301,57 @@
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O64" s="16" t="n">
-        <v>1242.9</v>
+        <v>484</v>
+      </c>
+      <c r="O64" s="15" t="n">
+        <v>572</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>80.19</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5369,64 +5361,64 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>484</v>
-      </c>
-      <c r="O65" s="12" t="n">
-        <v>572</v>
+        <v>700</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
-        <v>127.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5457,16 +5449,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5478,32 +5470,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5513,32 +5505,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>170</v>
+        <v>186.235</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5550,27 +5542,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5590,44 +5582,44 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.75</v>
+        <v>8</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>186.235</v>
-      </c>
-      <c r="O68" s="16" t="n">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="O68" s="15" t="n">
+        <v>465.85</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>0</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5637,12 +5629,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5662,59 +5654,59 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="O69" s="12" t="n">
-        <v>465.85</v>
+        <v>552</v>
+      </c>
+      <c r="O69" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>58.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5741,22 +5733,22 @@
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>552</v>
-      </c>
-      <c r="O70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5766,32 +5758,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5806,29 +5798,29 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O71" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5838,27 +5830,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5873,35 +5865,35 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O72" s="16" t="n">
-        <v>0</v>
+        <v>424.8</v>
       </c>
       <c r="P72" s="15" t="n">
         <v>0</v>
@@ -5910,27 +5902,27 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5961,19 +5953,19 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O73" s="16" t="n">
-        <v>424.8</v>
+        <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
@@ -5982,32 +5974,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6017,12 +6009,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6033,16 +6025,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>203.5</v>
+        <v>171.4</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6054,32 +6046,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6089,12 +6081,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6105,19 +6097,19 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>171.4</v>
+        <v>6177.52</v>
       </c>
       <c r="O75" s="16" t="n">
-        <v>0</v>
+        <v>2504.4</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
@@ -6126,32 +6118,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6166,7 +6158,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6177,16 +6169,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6198,32 +6190,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6233,74 +6225,74 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>6177.52</v>
-      </c>
-      <c r="O77" s="16" t="n">
-        <v>2504.4</v>
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>112.38</v>
       </c>
       <c r="P77" s="12" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr">
@@ -6310,29 +6302,21 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33401</t>
-        </is>
-      </c>
-      <c r="M78" s="14" t="inlineStr">
-        <is>
-          <t>00167624</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
       <c r="N78" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6342,32 +6326,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6382,93 +6366,101 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
-        <v>112.38</v>
+        <v>240</v>
+      </c>
+      <c r="O79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>56.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr"/>
-      <c r="M80" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33245</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>00166748</t>
+        </is>
+      </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>149</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6478,32 +6470,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6518,64 +6510,64 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>240</v>
+        <v>337.5</v>
       </c>
       <c r="O81" s="16" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="P81" s="12" t="n">
-        <v>0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6585,32 +6577,32 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>149</v>
+        <v>320</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6622,32 +6614,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6657,49 +6649,49 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>337.5</v>
-      </c>
-      <c r="O83" s="16" t="n">
-        <v>112.5</v>
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>1047</v>
       </c>
       <c r="P83" s="12" t="n">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6709,12 +6701,12 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6734,29 +6726,29 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>3.25</v>
+        <v>0.25</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>320</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6766,27 +6758,27 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6806,30 +6798,30 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K85" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
-        <v>1047</v>
+        <v>200</v>
+      </c>
+      <c r="O85" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
         <v>0</v>
@@ -6838,27 +6830,27 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6878,29 +6870,29 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6910,12 +6902,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6925,12 +6917,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6945,12 +6937,12 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
@@ -6961,16 +6953,16 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>200</v>
+        <v>680.8</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6982,32 +6974,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7017,34 +7009,34 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>2614.5</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7054,32 +7046,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7089,32 +7081,32 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>680.8</v>
+        <v>403.074</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7126,12 +7118,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7141,12 +7133,12 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7161,12 +7153,12 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
@@ -7177,19 +7169,19 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>2614.5</v>
-      </c>
-      <c r="O90" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>276</v>
       </c>
       <c r="P90" s="15" t="n">
         <v>0</v>
@@ -7198,12 +7190,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7213,12 +7205,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7238,27 +7230,27 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>403.074</v>
+        <v>142.1</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7270,27 +7262,27 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
@@ -7305,35 +7297,35 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
-        <v>276</v>
+        <v>11278.05</v>
+      </c>
+      <c r="O92" s="16" t="n">
+        <v>233.5</v>
       </c>
       <c r="P92" s="15" t="n">
         <v>0</v>
@@ -7342,12 +7334,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7357,12 +7349,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7382,27 +7374,27 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>142.1</v>
+        <v>1000</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7414,27 +7406,27 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
@@ -7454,7 +7446,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
@@ -7465,19 +7457,19 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>11278.05</v>
+        <v>220</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>233.5</v>
+        <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
         <v>0</v>
@@ -7486,32 +7478,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7521,12 +7513,12 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7537,16 +7529,16 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7558,32 +7550,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7593,64 +7585,64 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>220</v>
+        <v>910</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P96" s="15" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7670,7 +7662,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
@@ -7681,16 +7673,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>450</v>
+        <v>4050</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7702,32 +7694,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7737,64 +7729,64 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>910</v>
+        <v>1050</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>318.5</v>
+        <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -7814,7 +7806,7 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
@@ -7825,16 +7817,16 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>4050</v>
+        <v>433.5</v>
       </c>
       <c r="O99" s="16" t="n">
         <v>0</v>
@@ -7846,32 +7838,32 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -7881,34 +7873,34 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="15" t="n">
@@ -7918,12 +7910,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7933,12 +7925,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7953,12 +7945,12 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7969,16 +7961,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>433.5</v>
+        <v>285</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7990,12 +7982,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -8005,12 +7997,12 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
@@ -8025,12 +8017,12 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
@@ -8041,18 +8033,18 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8062,12 +8054,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8077,12 +8069,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8097,12 +8089,12 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
@@ -8113,16 +8105,16 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="O103" s="16" t="n">
         <v>0</v>
@@ -8134,32 +8126,32 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -8169,32 +8161,32 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>120</v>
+        <v>203.5</v>
       </c>
       <c r="O104" s="16" t="n">
         <v>0</v>
@@ -8206,12 +8198,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8221,12 +8213,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -8246,27 +8238,27 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K105" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8278,27 +8270,27 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -8313,12 +8305,12 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
@@ -8329,16 +8321,16 @@
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8350,32 +8342,32 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8385,12 +8377,12 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
@@ -8401,16 +8393,16 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>1088.5</v>
+        <v>130</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8422,12 +8414,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8437,12 +8429,12 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8462,7 +8454,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
@@ -8473,16 +8465,16 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O108" s="16" t="n">
         <v>0</v>
@@ -8494,12 +8486,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8509,12 +8501,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -8534,27 +8526,27 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="O109" s="16" t="n">
         <v>0</v>
@@ -8566,32 +8558,32 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -8601,32 +8593,32 @@
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="O110" s="16" t="n">
         <v>0</v>
@@ -8638,32 +8630,32 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
@@ -8673,34 +8665,34 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>255</v>
-      </c>
-      <c r="O111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8710,32 +8702,32 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -8745,32 +8737,32 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>140</v>
+        <v>204.14</v>
       </c>
       <c r="O112" s="16" t="n">
         <v>0</v>
@@ -8782,12 +8774,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8797,13 +8789,11 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Paramétrage interface Pastell</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v/>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8822,29 +8812,29 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O113" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8854,12 +8844,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8869,13 +8859,11 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v/>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -8889,34 +8877,34 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="15" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8926,27 +8914,27 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -8961,32 +8949,32 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>7.25</v>
+        <v>1.7</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>204.14</v>
+        <v>275</v>
       </c>
       <c r="O115" s="16" t="n">
         <v>0</v>
@@ -8998,12 +8986,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -9013,11 +9001,13 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -9031,28 +9021,28 @@
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9068,12 +9058,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9083,11 +9073,13 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9106,33 +9098,33 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>401.54</v>
+        <v>1290</v>
       </c>
       <c r="O117" s="16" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="P117" s="12" t="n">
-        <v>0</v>
+        <v>526.47</v>
       </c>
     </row>
     <row r="118">
@@ -9189,18 +9181,18 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>275</v>
-      </c>
-      <c r="O118" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9261,12 +9253,12 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9282,12 +9274,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9297,13 +9289,11 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v/>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
@@ -9322,44 +9312,44 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>1.7</v>
+        <v>4.25</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>1790</v>
+        <v>1000</v>
       </c>
       <c r="O120" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>526.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9369,13 +9359,11 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v/>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -9389,34 +9377,34 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="O121" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9426,27 +9414,27 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Déploiement LiEx</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -9466,23 +9454,23 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9498,22 +9486,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9531,59 +9519,59 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>4.25</v>
+        <v>10.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>1000</v>
+        <v>3016.08</v>
       </c>
       <c r="O123" s="16" t="n">
-        <v>0</v>
+        <v>2178.28</v>
       </c>
       <c r="P123" s="12" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9606,27 +9594,27 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>460</v>
+        <v>1200</v>
       </c>
       <c r="O124" s="16" t="n">
         <v>0</v>
@@ -9638,28 +9626,26 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v/>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9678,29 +9664,29 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="12" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O125" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9710,22 +9696,22 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9743,59 +9729,59 @@
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O126" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O126" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P126" s="15" t="n">
-        <v>207.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9813,34 +9799,34 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O127" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9850,12 +9836,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9865,7 +9851,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9888,29 +9874,29 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>3919.06</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="15" t="n">
@@ -9920,12 +9906,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9935,7 +9921,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9958,7 +9944,7 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
@@ -9969,12 +9955,12 @@
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -10039,12 +10025,12 @@
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10060,22 +10046,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10093,28 +10079,28 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10130,22 +10116,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10168,23 +10154,23 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
@@ -10200,12 +10186,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10215,7 +10201,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10233,34 +10219,34 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O133" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10270,12 +10256,12 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
@@ -10285,7 +10271,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10308,29 +10294,29 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="15" t="n">
@@ -10340,12 +10326,12 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10355,7 +10341,7 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10378,23 +10364,23 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
@@ -10410,22 +10396,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10443,34 +10429,34 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K136" s="14" t="n">
         <v>1</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="O136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="15" t="n">
@@ -10480,12 +10466,12 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -10495,11 +10481,13 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
@@ -10508,7 +10496,7 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -10518,29 +10506,21 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O137" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="12" t="n">
@@ -10550,22 +10530,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10578,35 +10558,27 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L138" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M138" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L138" s="14" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
       <c r="N138" s="15" t="n">
         <v>0</v>
       </c>
@@ -10620,12 +10592,12 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10635,7 +10607,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10648,7 +10620,7 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -10658,25 +10630,17 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K139" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L139" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M139" s="11" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+      <c r="L139" s="11" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr"/>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10690,61 +10654,67 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="n">
+        <v/>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr"/>
-      <c r="M140" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N140" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="15" t="n">
@@ -10754,22 +10724,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10782,7 +10752,7 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -10792,17 +10762,25 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr"/>
-      <c r="M141" s="11" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10816,22 +10794,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10849,16 +10827,16 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K142" s="14" t="n">
         <v>1</v>
@@ -10878,22 +10856,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10901,44 +10879,36 @@
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O143" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
@@ -10948,12 +10918,12 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
@@ -10963,7 +10933,7 @@
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10976,7 +10946,7 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr">
@@ -10986,25 +10956,17 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M144" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -11018,22 +10980,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11051,19 +11013,19 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11080,22 +11042,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11108,7 +11070,7 @@
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
@@ -11118,17 +11080,25 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr"/>
-      <c r="M146" s="14" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M146" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N146" s="15" t="n">
         <v>0</v>
       </c>
@@ -11142,22 +11112,22 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11173,21 +11143,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H147" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L147" s="11" t="inlineStr"/>
       <c r="M147" s="11" t="inlineStr"/>
@@ -11204,22 +11170,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11242,17 +11208,25 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr"/>
-      <c r="M148" s="14" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11266,12 +11240,12 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD06] Littéralis expert</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
@@ -11281,7 +11255,7 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11297,30 +11271,26 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H149" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M149" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N149" s="12" t="n">
@@ -11336,26 +11306,24 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C150" s="14" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
-        </is>
-      </c>
-      <c r="E150" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F150" s="14" t="inlineStr">
         <is>
@@ -11367,17 +11335,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H150" s="14" t="inlineStr"/>
+      <c r="H150" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="L150" s="14" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -11394,27 +11366,21 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E151" s="11" t="n">
-        <v/>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr"/>
       <c r="F151" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11422,35 +11388,23 @@
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H151" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L151" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M151" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
       <c r="N151" s="12" t="n">
         <v>0</v>
       </c>
@@ -11464,27 +11418,21 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
-        </is>
-      </c>
-      <c r="C152" s="14" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>COMMUNE DE VALENCAY</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
-        </is>
-      </c>
-      <c r="E152" s="14" t="n">
-        <v/>
-      </c>
+          <t>COMMUNE DE VALENCAY</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr"/>
       <c r="F152" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11492,31 +11440,23 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M152" s="14" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11530,25 +11470,21 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E153" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>VILLE DE BARRAUX</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11556,24 +11492,20 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H153" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L153" s="11" t="inlineStr"/>
       <c r="M153" s="11" t="inlineStr"/>
@@ -11590,18 +11522,18 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr"/>
@@ -11612,27 +11544,35 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K154" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L154" s="14" t="inlineStr"/>
-      <c r="M154" s="14" t="inlineStr"/>
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M154" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N154" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="O154" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P154" s="15" t="n">
@@ -11642,18 +11582,18 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr"/>
@@ -11670,11 +11610,11 @@
       <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K155" s="11" t="n">
         <v>0.25</v>
@@ -11694,18 +11634,18 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr"/>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr"/>
@@ -11716,23 +11656,31 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K156" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L156" s="14" t="inlineStr"/>
-      <c r="M156" s="14" t="inlineStr"/>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N156" s="15" t="n">
         <v>0</v>
       </c>
@@ -11746,18 +11694,18 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr"/>
@@ -11768,35 +11716,27 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L157" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M157" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L157" s="11" t="inlineStr"/>
+      <c r="M157" s="11" t="inlineStr"/>
       <c r="N157" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O157" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P157" s="12" t="n">
@@ -11806,18 +11746,18 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr"/>
@@ -11834,11 +11774,11 @@
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K158" s="14" t="n">
         <v>0.25</v>
@@ -11858,18 +11798,18 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11880,31 +11820,23 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M159" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr"/>
+      <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
@@ -11918,18 +11850,18 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11940,23 +11872,31 @@
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr"/>
-      <c r="M160" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M160" s="14" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
@@ -11970,18 +11910,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -11992,23 +11932,31 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N161" s="12" t="n">
         <v>0</v>
       </c>
@@ -12022,18 +11970,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12050,14 +11998,14 @@
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="L162" s="14" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -12074,18 +12022,18 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12102,23 +12050,23 @@
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34335</t>
+          <t>PDMDEP-30236</t>
         </is>
       </c>
       <c r="M163" s="11" t="inlineStr">
         <is>
-          <t>00168072</t>
+          <t>00152992</t>
         </is>
       </c>
       <c r="N163" s="12" t="n">
@@ -12134,18 +12082,18 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12156,31 +12104,23 @@
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L164" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M164" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="14" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
@@ -12194,18 +12134,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12216,23 +12156,31 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr"/>
-      <c r="M165" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
@@ -12246,18 +12194,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12274,14 +12222,14 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L166" s="14" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -12296,143 +12244,31 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="inlineStr">
-        <is>
-          <t>PSC-1047</t>
-        </is>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C167" s="11" t="inlineStr"/>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr"/>
-      <c r="F167" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G167" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H167" s="11" t="inlineStr"/>
-      <c r="I167" s="11" t="inlineStr">
-        <is>
-          <t>04/11/2025</t>
-        </is>
-      </c>
-      <c r="J167" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K167" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L167" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M167" s="11" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
-      <c r="N167" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="13" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B168" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C168" s="14" t="inlineStr"/>
-      <c r="D168" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E168" s="14" t="inlineStr"/>
-      <c r="F168" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G168" s="14" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H168" s="14" t="inlineStr"/>
-      <c r="I168" s="14" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J168" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K168" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L168" s="14" t="inlineStr"/>
-      <c r="M168" s="14" t="inlineStr"/>
-      <c r="N168" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="17" t="inlineStr">
+      <c r="A167" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B169" s="17" t="inlineStr"/>
-      <c r="C169" s="17" t="inlineStr"/>
-      <c r="D169" s="17" t="inlineStr"/>
-      <c r="E169" s="17" t="inlineStr"/>
-      <c r="F169" s="17" t="inlineStr"/>
-      <c r="G169" s="17" t="inlineStr"/>
-      <c r="H169" s="17" t="inlineStr"/>
-      <c r="I169" s="17" t="inlineStr"/>
-      <c r="J169" s="17" t="inlineStr"/>
-      <c r="K169" s="17" t="inlineStr"/>
-      <c r="L169" s="17" t="inlineStr"/>
-      <c r="M169" s="17" t="inlineStr"/>
-      <c r="N169" s="18" t="n">
-        <v>116825.667</v>
-      </c>
-      <c r="O169" s="18" t="n">
-        <v>32201.802</v>
-      </c>
-      <c r="P169" s="18" t="n">
-        <v>137.42</v>
+      <c r="B167" s="17" t="inlineStr"/>
+      <c r="C167" s="17" t="inlineStr"/>
+      <c r="D167" s="17" t="inlineStr"/>
+      <c r="E167" s="17" t="inlineStr"/>
+      <c r="F167" s="17" t="inlineStr"/>
+      <c r="G167" s="17" t="inlineStr"/>
+      <c r="H167" s="17" t="inlineStr"/>
+      <c r="I167" s="17" t="inlineStr"/>
+      <c r="J167" s="17" t="inlineStr"/>
+      <c r="K167" s="17" t="inlineStr"/>
+      <c r="L167" s="17" t="inlineStr"/>
+      <c r="M167" s="17" t="inlineStr"/>
+      <c r="N167" s="18" t="n">
+        <v>99948.33499999999</v>
+      </c>
+      <c r="O167" s="18" t="n">
+        <v>34839.002</v>
+      </c>
+      <c r="P167" s="18" t="n">
+        <v>143.32</v>
       </c>
     </row>
   </sheetData>
@@ -12600,8 +12436,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13791,7 +13625,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>159</v>
+        <v>160.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>19.25</v>
@@ -13800,17 +13634,17 @@
         <v>8.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>186.33</v>
+        <v>188.08</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>29.75</v>
+        <v>31.75</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
     </row>
@@ -13821,16 +13655,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>37.75</v>
+        <v>40.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>10.25</v>
+        <v>14.75</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -13840,7 +13674,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -13937,16 +13771,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>485063</v>
+        <v>483273</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>202420</v>
+        <v>200860</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>282643</v>
+        <v>282413</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>224307</v>
+        <v>224077</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -13962,16 +13796,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>256624</v>
+        <v>255734</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>67787</v>
+        <v>67127</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>188837</v>
+        <v>188607</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>169625</v>
+        <v>169395</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -13987,10 +13821,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>225339</v>
+        <v>224439</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>131533</v>
+        <v>130633</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>93806</v>
@@ -14269,7 +14103,7 @@
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -14875,7 +14709,7 @@
         </is>
       </c>
       <c r="I22" s="24" t="n">
-        <v>17313</v>
+        <v>17813</v>
       </c>
     </row>
     <row r="23">
@@ -14917,7 +14751,7 @@
         </is>
       </c>
       <c r="I24" s="24" t="n">
-        <v>5285</v>
+        <v>5785</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-20.xlsx
+++ b/jira_export_2026-10-20.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>34,839 €</t>
+          <t>35,100 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>11,173 €</t>
+          <t>11,223 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>365 h</t>
+          <t>367 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5530,9 +5530,9 @@
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>186.235</v>
-      </c>
-      <c r="O67" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5674,9 +5674,9 @@
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>552</v>
-      </c>
-      <c r="O69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5974,32 +5974,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6025,19 +6025,19 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>171.4</v>
+        <v>6177.52</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>0</v>
+        <v>2504.4</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6097,19 +6097,19 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>6177.52</v>
+        <v>500</v>
       </c>
       <c r="O75" s="16" t="n">
-        <v>2504.4</v>
+        <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
@@ -6118,32 +6118,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6158,44 +6158,44 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O76" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
+        <v>112.38</v>
       </c>
       <c r="P76" s="15" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -6230,69 +6230,61 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L77" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33315</t>
-        </is>
-      </c>
-      <c r="M77" s="11" t="inlineStr">
-        <is>
-          <t>00167138</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="12" t="n">
-        <v>112.38</v>
+        <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
-        <v>56.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr">
@@ -6302,21 +6294,29 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr"/>
-      <c r="M78" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33272</t>
+        </is>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>00166910</t>
+        </is>
+      </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6326,27 +6326,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6377,16 +6377,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>240</v>
+        <v>149</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6398,32 +6398,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6433,38 +6433,38 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>149</v>
+        <v>337.5</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="81">
@@ -6521,53 +6521,53 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>337.5</v>
+        <v>320</v>
       </c>
       <c r="O81" s="16" t="n">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6577,35 +6577,35 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>320</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>1047</v>
       </c>
       <c r="P82" s="15" t="n">
         <v>0</v>
@@ -6614,32 +6614,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6649,35 +6649,35 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="12" t="n">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
         <v>0</v>
@@ -6686,32 +6686,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -6733,22 +6733,22 @@
         <v>6</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6758,32 +6758,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6793,34 +6793,34 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="O85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6830,32 +6830,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
@@ -6877,22 +6877,22 @@
         <v>6</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
+        <v>680.8</v>
+      </c>
+      <c r="O86" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6902,12 +6902,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6937,32 +6937,32 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>680.8</v>
+        <v>2614.5</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6974,32 +6974,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7009,34 +7009,34 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>2614.5</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7046,32 +7046,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -7093,23 +7093,23 @@
         <v>6</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>403.074</v>
-      </c>
-      <c r="O89" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>276</v>
       </c>
       <c r="P89" s="12" t="n">
         <v>0</v>
@@ -7118,27 +7118,27 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7153,35 +7153,35 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
-        <v>276</v>
+        <v>11278.05</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>233.5</v>
       </c>
       <c r="P90" s="15" t="n">
         <v>0</v>
@@ -7190,32 +7190,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7225,32 +7225,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>142.1</v>
+        <v>220</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7262,27 +7262,27 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
@@ -7313,19 +7313,19 @@
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>11278.05</v>
+        <v>450</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>233.5</v>
+        <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
         <v>0</v>
@@ -7334,27 +7334,27 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7374,59 +7374,59 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="O93" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P93" s="12" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
@@ -7457,16 +7457,16 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>220</v>
+        <v>4050</v>
       </c>
       <c r="O94" s="16" t="n">
         <v>0</v>
@@ -7478,27 +7478,27 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7529,16 +7529,16 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>450</v>
+        <v>1050</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7550,32 +7550,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7585,69 +7585,69 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>910</v>
+        <v>433.5</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>318.5</v>
+        <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7657,34 +7657,34 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>4050</v>
-      </c>
-      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7694,27 +7694,27 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
@@ -7745,16 +7745,16 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>1050</v>
+        <v>285</v>
       </c>
       <c r="O98" s="16" t="n">
         <v>0</v>
@@ -7766,32 +7766,32 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="O99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7838,32 +7838,32 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -7873,34 +7873,34 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="15" t="n">
+        <v>210</v>
+      </c>
+      <c r="O100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="15" t="n">
@@ -7910,27 +7910,27 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7945,32 +7945,32 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>285</v>
+        <v>203.5</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7982,32 +7982,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8017,32 +8017,32 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O102" s="16" t="n">
         <v>0</v>
@@ -8054,12 +8054,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8094,23 +8094,23 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K103" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8126,27 +8126,27 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
@@ -8177,16 +8177,16 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>203.5</v>
+        <v>130</v>
       </c>
       <c r="O104" s="16" t="n">
         <v>0</v>
@@ -8198,12 +8198,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
@@ -8249,16 +8249,16 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8270,12 +8270,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K106" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8342,32 +8342,32 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8377,32 +8377,32 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8414,32 +8414,32 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -8449,34 +8449,34 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>255</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8486,32 +8486,32 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -8521,34 +8521,34 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="O109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8558,12 +8558,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8573,13 +8573,11 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
-        </is>
-      </c>
-      <c r="E110" s="14" t="inlineStr">
-        <is>
-          <t>Paramétrage interface Pastell</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v/>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -8598,29 +8596,29 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8630,12 +8628,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8645,12 +8643,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -8665,34 +8663,34 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O111" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8702,27 +8700,27 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
@@ -8737,34 +8735,34 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>7.25</v>
+        <v>1.7</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8774,12 +8772,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8789,11 +8787,13 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8807,49 +8807,49 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
-        <v>0</v>
+        <v>1290</v>
+      </c>
+      <c r="O113" s="16" t="n">
+        <v>895</v>
       </c>
       <c r="P113" s="12" t="n">
-        <v>0</v>
+        <v>526.47</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8859,11 +8859,13 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -8882,29 +8884,29 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8965,18 +8967,18 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>275</v>
-      </c>
-      <c r="O115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8986,12 +8988,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -9001,13 +9003,11 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v/>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -9026,29 +9026,29 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1.7</v>
+        <v>4.25</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9058,12 +9058,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9073,13 +9073,11 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v/>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9093,64 +9091,64 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>1290</v>
+        <v>460</v>
       </c>
       <c r="O117" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
-        <v>526.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Déploiement LiEx</t>
         </is>
       </c>
       <c r="F118" s="14" t="inlineStr">
@@ -9170,23 +9168,23 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9202,28 +9200,26 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v/>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9237,59 +9233,59 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="12" t="n">
-        <v>0</v>
+        <v>3016.08</v>
+      </c>
+      <c r="O119" s="16" t="n">
+        <v>2178.28</v>
       </c>
       <c r="P119" s="12" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9307,34 +9303,34 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>4.25</v>
+        <v>0.75</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
@@ -9344,12 +9340,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9359,7 +9355,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9377,34 +9373,34 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="O121" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9414,28 +9410,26 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE BAGNOLET</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v/>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
@@ -9454,23 +9448,23 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9486,22 +9480,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9519,59 +9513,59 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O123" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
-        <v>207.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9589,34 +9583,34 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9626,12 +9620,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9641,7 +9635,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9664,29 +9658,29 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
-        <v>3919.06</v>
-      </c>
-      <c r="O125" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9696,12 +9690,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9711,7 +9705,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9734,7 +9728,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
@@ -9745,12 +9739,12 @@
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
@@ -9766,22 +9760,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9799,28 +9793,28 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9836,22 +9830,22 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9874,23 +9868,23 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
@@ -9906,12 +9900,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9921,7 +9915,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9939,34 +9933,34 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O129" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
@@ -9976,22 +9970,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10014,23 +10008,23 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K130" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10046,12 +10040,12 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10061,7 +10055,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10079,28 +10073,28 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10116,12 +10110,12 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
@@ -10131,11 +10125,13 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
-        </is>
-      </c>
-      <c r="E132" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
@@ -10144,35 +10140,27 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M132" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10186,12 +10174,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10201,7 +10189,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10214,7 +10202,7 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -10224,29 +10212,21 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M133" s="11" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O133" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10256,12 +10236,12 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
@@ -10271,7 +10251,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10284,39 +10264,31 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M134" s="14" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
       <c r="N134" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="15" t="n">
@@ -10326,22 +10298,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10349,7 +10321,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -10359,34 +10331,34 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O135" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="12" t="n">
@@ -10396,12 +10368,12 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10411,7 +10383,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10429,28 +10401,28 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
@@ -10466,28 +10438,26 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CD Manche</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v/>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
@@ -10506,14 +10476,14 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L137" s="11" t="inlineStr"/>
       <c r="M137" s="11" t="inlineStr"/>
@@ -10530,12 +10500,12 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
@@ -10545,7 +10515,7 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10568,14 +10538,14 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10592,12 +10562,12 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10607,7 +10577,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10625,19 +10595,19 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10654,22 +10624,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10677,44 +10647,36 @@
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M140" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O140" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="15" t="n">
@@ -10724,12 +10686,12 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10739,7 +10701,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10762,23 +10724,23 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N141" s="12" t="n">
@@ -10794,12 +10756,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10809,7 +10771,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10825,21 +10787,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H142" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H142" s="14" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1</v>
+        <v>2.75</v>
       </c>
       <c r="L142" s="14" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -10856,12 +10814,12 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
@@ -10871,7 +10829,7 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10889,22 +10847,30 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10918,12 +10884,12 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD06] Littéralis expert</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
@@ -10933,7 +10899,7 @@
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10946,27 +10912,31 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H144" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K144" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -10980,26 +10950,24 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr"/>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
@@ -11018,14 +10986,14 @@
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11042,27 +11010,21 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
-        </is>
-      </c>
-      <c r="C146" s="14" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr"/>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
-        </is>
-      </c>
-      <c r="E146" s="14" t="n">
-        <v/>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr"/>
       <c r="F146" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11070,35 +11032,23 @@
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H146" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="inlineStr"/>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M146" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
       <c r="N146" s="15" t="n">
         <v>0</v>
       </c>
@@ -11112,56 +11062,46 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C147" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>CD 56 MORBIHAN</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F147" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr"/>
+      <c r="D147" s="11" t="inlineStr"/>
+      <c r="E147" s="11" t="inlineStr"/>
+      <c r="F147" s="11" t="inlineStr"/>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O147" s="12" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P147" s="12" t="n">
         <v>0</v>
@@ -11170,27 +11110,21 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C148" s="14" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>COMMUNE DE VALENCAY</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr"/>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E148" s="14" t="n">
-        <v/>
-      </c>
+          <t>COMMUNE DE VALENCAY</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr"/>
       <c r="F148" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11198,35 +11132,23 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H148" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H148" s="14" t="inlineStr"/>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M148" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11240,27 +11162,21 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
-        </is>
-      </c>
-      <c r="C149" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>VILLE DE BARRAUX</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
-        </is>
-      </c>
-      <c r="E149" s="11" t="n">
-        <v/>
-      </c>
+          <t>VILLE DE BARRAUX</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr"/>
       <c r="F149" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11268,31 +11184,23 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M149" s="11" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr"/>
       <c r="N149" s="12" t="n">
         <v>0</v>
       </c>
@@ -11306,25 +11214,21 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E150" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr"/>
       <c r="F150" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11332,52 +11236,56 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H150" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L150" s="14" t="inlineStr"/>
-      <c r="M150" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M150" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N150" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="15" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O150" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P150" s="15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr"/>
@@ -11394,11 +11302,11 @@
       <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K151" s="11" t="n">
         <v>0.25</v>
@@ -11418,18 +11326,18 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr"/>
@@ -11440,23 +11348,31 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K152" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L152" s="14" t="inlineStr"/>
-      <c r="M152" s="14" t="inlineStr"/>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11470,18 +11386,18 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr"/>
@@ -11498,14 +11414,14 @@
       <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L153" s="11" t="inlineStr"/>
       <c r="M153" s="11" t="inlineStr"/>
@@ -11522,18 +11438,18 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr"/>
@@ -11544,35 +11460,27 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K154" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L154" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M154" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L154" s="14" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
       <c r="N154" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O154" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P154" s="15" t="n">
@@ -11582,18 +11490,18 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr"/>
@@ -11610,14 +11518,14 @@
       <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="L155" s="11" t="inlineStr"/>
       <c r="M155" s="11" t="inlineStr"/>
@@ -11634,18 +11542,18 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr"/>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr"/>
@@ -11662,23 +11570,23 @@
       <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K156" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34778</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M156" s="14" t="inlineStr">
         <is>
-          <t>00172868</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N156" s="15" t="n">
@@ -11694,18 +11602,18 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr"/>
@@ -11716,23 +11624,31 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K157" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="inlineStr"/>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N157" s="12" t="n">
         <v>0</v>
       </c>
@@ -11746,18 +11662,18 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr"/>
@@ -11774,11 +11690,11 @@
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K158" s="14" t="n">
         <v>0.25</v>
@@ -11798,18 +11714,18 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11820,23 +11736,31 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr"/>
-      <c r="M159" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-30236</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>00152992</t>
+        </is>
+      </c>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
@@ -11850,18 +11774,18 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11872,31 +11796,23 @@
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K160" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L160" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M160" s="14" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+      <c r="L160" s="14" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
@@ -11910,18 +11826,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -11938,23 +11854,23 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K161" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M161" s="11" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N161" s="12" t="n">
@@ -11970,18 +11886,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -11998,14 +11914,14 @@
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L162" s="14" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -12020,255 +11936,31 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>PSC-1119</t>
-        </is>
-      </c>
-      <c r="B163" s="11" t="inlineStr">
-        <is>
-          <t>BETSCHDORF</t>
-        </is>
-      </c>
-      <c r="C163" s="11" t="inlineStr"/>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>BETSCHDORF</t>
-        </is>
-      </c>
-      <c r="E163" s="11" t="inlineStr"/>
-      <c r="F163" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G163" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H163" s="11" t="inlineStr"/>
-      <c r="I163" s="11" t="inlineStr">
-        <is>
-          <t>16/01/2026</t>
-        </is>
-      </c>
-      <c r="J163" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="K163" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L163" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M163" s="11" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
-      <c r="N163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="13" t="inlineStr">
-        <is>
-          <t>PSC-1060</t>
-        </is>
-      </c>
-      <c r="B164" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE DE COUBLEVIE</t>
-        </is>
-      </c>
-      <c r="C164" s="14" t="inlineStr"/>
-      <c r="D164" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE DE COUBLEVIE</t>
-        </is>
-      </c>
-      <c r="E164" s="14" t="inlineStr"/>
-      <c r="F164" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G164" s="14" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H164" s="14" t="inlineStr"/>
-      <c r="I164" s="14" t="inlineStr">
-        <is>
-          <t>12/11/2025</t>
-        </is>
-      </c>
-      <c r="J164" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K164" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L164" s="14" t="inlineStr"/>
-      <c r="M164" s="14" t="inlineStr"/>
-      <c r="N164" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="10" t="inlineStr">
-        <is>
-          <t>PSC-1047</t>
-        </is>
-      </c>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C165" s="11" t="inlineStr"/>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="E165" s="11" t="inlineStr"/>
-      <c r="F165" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G165" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H165" s="11" t="inlineStr"/>
-      <c r="I165" s="11" t="inlineStr">
-        <is>
-          <t>04/11/2025</t>
-        </is>
-      </c>
-      <c r="J165" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K165" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M165" s="11" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
-      <c r="N165" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="13" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B166" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C166" s="14" t="inlineStr"/>
-      <c r="D166" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E166" s="14" t="inlineStr"/>
-      <c r="F166" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G166" s="14" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H166" s="14" t="inlineStr"/>
-      <c r="I166" s="14" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J166" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K166" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L166" s="14" t="inlineStr"/>
-      <c r="M166" s="14" t="inlineStr"/>
-      <c r="N166" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="17" t="inlineStr">
+      <c r="A163" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B167" s="17" t="inlineStr"/>
-      <c r="C167" s="17" t="inlineStr"/>
-      <c r="D167" s="17" t="inlineStr"/>
-      <c r="E167" s="17" t="inlineStr"/>
-      <c r="F167" s="17" t="inlineStr"/>
-      <c r="G167" s="17" t="inlineStr"/>
-      <c r="H167" s="17" t="inlineStr"/>
-      <c r="I167" s="17" t="inlineStr"/>
-      <c r="J167" s="17" t="inlineStr"/>
-      <c r="K167" s="17" t="inlineStr"/>
-      <c r="L167" s="17" t="inlineStr"/>
-      <c r="M167" s="17" t="inlineStr"/>
-      <c r="N167" s="18" t="n">
-        <v>99948.33499999999</v>
-      </c>
-      <c r="O167" s="18" t="n">
-        <v>34839.002</v>
-      </c>
-      <c r="P167" s="18" t="n">
-        <v>143.32</v>
+      <c r="B163" s="17" t="inlineStr"/>
+      <c r="C163" s="17" t="inlineStr"/>
+      <c r="D163" s="17" t="inlineStr"/>
+      <c r="E163" s="17" t="inlineStr"/>
+      <c r="F163" s="17" t="inlineStr"/>
+      <c r="G163" s="17" t="inlineStr"/>
+      <c r="H163" s="17" t="inlineStr"/>
+      <c r="I163" s="17" t="inlineStr"/>
+      <c r="J163" s="17" t="inlineStr"/>
+      <c r="K163" s="17" t="inlineStr"/>
+      <c r="L163" s="17" t="inlineStr"/>
+      <c r="M163" s="17" t="inlineStr"/>
+      <c r="N163" s="18" t="n">
+        <v>91418.78599999999</v>
+      </c>
+      <c r="O163" s="18" t="n">
+        <v>35099.802</v>
+      </c>
+      <c r="P163" s="18" t="n">
+        <v>143.66</v>
       </c>
     </row>
   </sheetData>
@@ -12432,10 +12124,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13625,7 +13313,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>160.75</v>
+        <v>162</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>19.25</v>
@@ -13634,7 +13322,7 @@
         <v>8.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>188.08</v>
+        <v>189.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>31.75</v>
@@ -13644,7 +13332,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
     </row>
@@ -13771,10 +13459,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>483273</v>
+        <v>483012</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>200860</v>
+        <v>200599</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>282413</v>
@@ -13796,10 +13484,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>255734</v>
+        <v>255473</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>67127</v>
+        <v>66866</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>188607</v>
